--- a/BOM/Black Body.xlsx
+++ b/BOM/Black Body.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kellh\Documents\LHR\BlackBody\Power-Generation-Blackbody\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06BBC04-8C5D-4231-8B17-0371AD0614F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="98" yWindow="630" windowWidth="21599" windowHeight="12353" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,253 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="80">
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>DNP</t>
+  </si>
+  <si>
+    <t>Exclude from BOM</t>
+  </si>
+  <si>
+    <t>Exclude from Board</t>
+  </si>
+  <si>
+    <t>Footprint</t>
+  </si>
+  <si>
+    <t>Datasheet</t>
+  </si>
+  <si>
+    <t>P/N</t>
+  </si>
+  <si>
+    <t>Alert_1,Alert_2</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>LED_SMD:LED_0603_1608Metric_Pad1.05x0.95mm_HandSolder</t>
+  </si>
+  <si>
+    <t>~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LS Q976.01-N1Q2-1 </t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>Capacitor_SMD:C_0805_2012Metric_Pad1.18x1.45mm_HandSolder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLASU168SB5105KTNA01 </t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>0.1u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLASH168SB7104KTNA01 </t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>Fuse:Fuseholder_Blade_Mini_Keystone_3568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3557-2 </t>
+  </si>
+  <si>
+    <t>FB1,FB2</t>
+  </si>
+  <si>
+    <t>Inductor_SMD:L_0603_1608Metric_Pad1.05x0.95mm_HandSolder</t>
+  </si>
+  <si>
+    <t>GND1,Irrad_Fuse1,TP_TC_1,TP_TC_2,TP_TC_F_1,TP_TC_F_2,VCC1</t>
+  </si>
+  <si>
+    <t>TestPoint</t>
+  </si>
+  <si>
+    <t>TestPoint:TestPoint_Keystone_5005-5009_Compact</t>
+  </si>
+  <si>
+    <t>IC2</t>
+  </si>
+  <si>
+    <t>MCP96L00T-E_MX</t>
+  </si>
+  <si>
+    <t>BlackBody:QFN65P500X500X100-21N-D</t>
+  </si>
+  <si>
+    <t>https://datasheet.datasheetarchive.com/originals/distributors/DKDS41/DSANUWW0026539.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCP96L00T-E/MX </t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>53307-2471</t>
+  </si>
+  <si>
+    <t>utsvt_connectors:PeripheralSOM</t>
+  </si>
+  <si>
+    <t>https://www.molex.com/en-us/products/part-detail-pdf/533072471?display=pdf</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>Conn_01x02</t>
+  </si>
+  <si>
+    <t>utsvt_connectors:105313-2102</t>
+  </si>
+  <si>
+    <t>C17189968</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>LogicAnalyzer</t>
+  </si>
+  <si>
+    <t>utsvt_connectors:CONN_SFH11-xxxC-D05-ST-XX_SUL</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/sullins-connector-solutions/SFH11-PBPC-D05-ST-BK/1990087?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=120565755&amp;gbraid=0AAAAADrbLljEsXDDEt5svizMM4jeYrL-A&amp;gclid=Cj0KCQjwwZDFBhCpARIsAB95qO2YCKMg2VQme3QQBBCFa3dTLVMMS-qCbMZE8KZJpYe-_Bi6ULwi-x0aAvv3EALw_wcB</t>
+  </si>
+  <si>
+    <t>SFH11-PBPC-D05-ST-BK</t>
+  </si>
+  <si>
+    <t>J5</t>
+  </si>
+  <si>
+    <t>Conn_02x04_Top_Bottom</t>
+  </si>
+  <si>
+    <t>Connector_Molex:Molex_Nano-Fit_105314-xx08_2x04_P2.50mm_Horizontal</t>
+  </si>
+  <si>
+    <t>C841208</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>Conn_02x03_Top_Bottom</t>
+  </si>
+  <si>
+    <t>utsvt_connectors:105314-1306</t>
+  </si>
+  <si>
+    <t>C493437</t>
+  </si>
+  <si>
+    <t>LOGO1</t>
+  </si>
+  <si>
+    <t>Dr. Hallock</t>
+  </si>
+  <si>
+    <t>utsvt_logos:LHRs_LOGO</t>
+  </si>
+  <si>
+    <t>LOGO2</t>
+  </si>
+  <si>
+    <t>utsvt_logos:Hallock_Image_Tiny</t>
+  </si>
+  <si>
+    <t>R1,R2,R3,R11,R15,R16</t>
+  </si>
+  <si>
+    <t>10k</t>
+  </si>
+  <si>
+    <t>Resistor_SMD:R_0603_1608Metric_Pad0.98x0.95mm_HandSolder</t>
+  </si>
+  <si>
+    <t>CRCW060310K0FKEI  ,CRCW06031K00FKEI  ,CRCW080510K0FKEA</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>0603WAF1004T5E</t>
+  </si>
+  <si>
+    <t>R5,R6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW0603100RFKEA </t>
+  </si>
+  <si>
+    <t>R7,R8</t>
+  </si>
+  <si>
+    <t>2M</t>
+  </si>
+  <si>
+    <t>0603WAF2004T5E</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW06030000Z0EE </t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>43k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW060343K0FKEI </t>
+  </si>
+  <si>
+    <t>R13,R14</t>
+  </si>
+  <si>
+    <t>1k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRCW08051K50FKEA </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +581,455 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="22.06640625" customWidth="1"/>
+    <col min="7" max="7" width="61.73046875" customWidth="1"/>
+    <col min="8" max="8" width="16.59765625" customWidth="1"/>
+    <col min="9" max="9" width="22.796875" customWidth="1"/>
+    <col min="10" max="10" width="27.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>200</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>742792910</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>5015</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>100</v>
+      </c>
+      <c r="G18" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>